--- a/rosa_summary.xlsx
+++ b/rosa_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -938,50 +938,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>2</v>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>2</v>
       </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
         <v>1</v>
       </c>
@@ -998,6 +978,298 @@
         <v>3</v>
       </c>
       <c r="AH10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH18" t="n">
         <v>3</v>
       </c>
     </row>

--- a/rosa_summary.xlsx
+++ b/rosa_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,6 +814,2823 @@
         <v>3</v>
       </c>
       <c r="AI3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-11-10 14:40:11</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:19:00</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:20:40</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:21:09</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:21:19</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:21:29</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:21:50</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:22:00</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:22:20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:22:30</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:22:41</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:23:01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:23:11</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:23:42</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:23:52</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:24:02</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:24:13</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:24:23</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:24:44</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:24:54</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:25:04</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:25:14</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:25:35</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:25:55</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-11-10 15:26:06</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI28" t="n">
         <v>3</v>
       </c>
     </row>

--- a/rosa_summary.xlsx
+++ b/rosa_summary.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROSA" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AJ121"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="27.21875" customWidth="1" min="35" max="35"/>
+    <col width="52.77734375" customWidth="1" min="36" max="36"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -11918,6 +11921,2298 @@
       </c>
       <c r="AJ101" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:02:54</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>2</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:03:22</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>2</v>
+      </c>
+      <c r="M103" t="n">
+        <v>2</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>2</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:03:42</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>2</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:04:24</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>2</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:05:34</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>2</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>2</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:05:45</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>2</v>
+      </c>
+      <c r="M107" t="n">
+        <v>2</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>2</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>2</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:11:54</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:12:04</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2</v>
+      </c>
+      <c r="M109" t="n">
+        <v>2</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>2</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:14:43</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" t="n">
+        <v>2</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>2</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>2</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>2</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>2</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:14:53</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>2</v>
+      </c>
+      <c r="M111" t="n">
+        <v>2</v>
+      </c>
+      <c r="N111" t="n">
+        <v>1</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>2</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:21:55</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>2</v>
+      </c>
+      <c r="M112" t="n">
+        <v>2</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>2</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ112" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:22:05</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>2</v>
+      </c>
+      <c r="M113" t="n">
+        <v>2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>2</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:22:15</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" t="n">
+        <v>2</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>2</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ114" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:22:25</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2</v>
+      </c>
+      <c r="M115" t="n">
+        <v>2</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>2</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ115" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:22:36</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>2</v>
+      </c>
+      <c r="M116" t="n">
+        <v>2</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>2</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ116" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:22:46</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>2</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>2</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:22:56</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>2</v>
+      </c>
+      <c r="M118" t="n">
+        <v>2</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>2</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:23:06</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>2</v>
+      </c>
+      <c r="M119" t="n">
+        <v>2</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>2</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:23:16</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>2</v>
+      </c>
+      <c r="M120" t="n">
+        <v>2</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>2</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-11-21 13:23:27</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>2</v>
+      </c>
+      <c r="M121" t="n">
+        <v>2</v>
+      </c>
+      <c r="N121" t="n">
+        <v>1</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>2</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
